--- a/Outputs/Scenarios/PtX_demand_FR_Electrification.xlsx
+++ b/Outputs/Scenarios/PtX_demand_FR_Electrification.xlsx
@@ -532,7 +532,7 @@
         <v>2030</v>
       </c>
       <c r="C3" t="n">
-        <v>0.004874654208608501</v>
+        <v>0.0048746542086085</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -840,7 +840,7 @@
         <v>0.8151922188048346</v>
       </c>
       <c r="G11" t="n">
-        <v>0.008573041577827002</v>
+        <v>0.008573041577827</v>
       </c>
       <c r="H11" t="n">
         <v>0.1450582004686673</v>
@@ -1571,7 +1571,7 @@
         <v>0.0165448424154421</v>
       </c>
       <c r="D31" t="n">
-        <v>0.006344688344038171</v>
+        <v>0.006344688344038173</v>
       </c>
       <c r="E31" t="n">
         <v>0.0259660839994584</v>
@@ -1592,7 +1592,7 @@
         <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>0.006263914809929811</v>
+        <v>0.00626391480992981</v>
       </c>
     </row>
     <row r="32">
@@ -1629,7 +1629,7 @@
         <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>0.02505565923971925</v>
+        <v>0.02505565923971924</v>
       </c>
     </row>
     <row r="33">
@@ -1645,7 +1645,7 @@
         <v>0</v>
       </c>
       <c r="D33" t="n">
-        <v>0.006633844584230426</v>
+        <v>0.006633844584230428</v>
       </c>
       <c r="E33" t="n">
         <v>0</v>
@@ -1999,7 +1999,7 @@
         <v>0.0004970923031374797</v>
       </c>
       <c r="K42" t="n">
-        <v>0.006263914809929811</v>
+        <v>0.00626391480992981</v>
       </c>
     </row>
     <row r="43">

--- a/Outputs/Scenarios/PtX_demand_FR_Electrification.xlsx
+++ b/Outputs/Scenarios/PtX_demand_FR_Electrification.xlsx
@@ -1037,7 +1037,7 @@
         <v>0.006379959808676661</v>
       </c>
       <c r="K16" t="n">
-        <v>0.006437944759309748</v>
+        <v>0.007716057101497999</v>
       </c>
     </row>
     <row r="17">
@@ -1074,7 +1074,7 @@
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>0.001072990793218291</v>
+        <v>0.001335227694788333</v>
       </c>
     </row>
     <row r="18">
@@ -1111,7 +1111,7 @@
         <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>0.004291963172873166</v>
+        <v>0.005340910779153334</v>
       </c>
     </row>
     <row r="19">
@@ -1148,7 +1148,7 @@
         <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>0.006437944759309748</v>
+        <v>0.005340910779153334</v>
       </c>
     </row>
     <row r="20">
@@ -1333,7 +1333,7 @@
         <v>0.0005112911688710039</v>
       </c>
       <c r="K24" t="n">
-        <v>0.009265169789572248</v>
+        <v>0.009096149444370491</v>
       </c>
     </row>
     <row r="25">
@@ -1370,7 +1370,7 @@
         <v>0.00309484652084073</v>
       </c>
       <c r="K25" t="n">
-        <v>0.08691105242122352</v>
+        <v>0.08532557299497316</v>
       </c>
     </row>
     <row r="26">
@@ -1481,7 +1481,7 @@
         <v>9.192442138230554e-05</v>
       </c>
       <c r="K28" t="n">
-        <v>0.001072990793218291</v>
+        <v>0.001335227694788333</v>
       </c>
     </row>
     <row r="29">
@@ -1555,7 +1555,7 @@
         <v>0.009444753759612115</v>
       </c>
       <c r="K30" t="n">
-        <v>0.03758348885957886</v>
+        <v>0.04129367971396962</v>
       </c>
     </row>
     <row r="31">
@@ -1592,7 +1592,7 @@
         <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>0.00626391480992981</v>
+        <v>0.007145678686476698</v>
       </c>
     </row>
     <row r="32">
@@ -1629,7 +1629,7 @@
         <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>0.02505565923971924</v>
+        <v>0.02858271474590679</v>
       </c>
     </row>
     <row r="33">
@@ -1666,7 +1666,7 @@
         <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>0.03758348885957886</v>
+        <v>0.02858271474590679</v>
       </c>
     </row>
     <row r="34">
@@ -1999,7 +1999,7 @@
         <v>0.0004970923031374797</v>
       </c>
       <c r="K42" t="n">
-        <v>0.00626391480992981</v>
+        <v>0.007145678686476698</v>
       </c>
     </row>
     <row r="43">
